--- a/面试结果汇总表.xlsx
+++ b/面试结果汇总表.xlsx
@@ -543,17 +543,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>刘芳</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>数学</t>
+          <t>语文</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>云南昭通某小学</t>
+          <t>云南红河某小学</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -577,12 +577,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>周明</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>语文</t>
+          <t>数学</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>吴婷</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>贵州毕节某小学</t>
+          <t>贵州黔东南某小学</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -649,17 +649,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>郑强</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>数学</t>
+          <t>体育</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>甘肃会宁某小学</t>
+          <t>甘肃定西某小学</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>陈七</t>
+          <t>孙悦</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>科学</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
